--- a/backend/data/financials_by_company/0712.HK.xlsx
+++ b/backend/data/financials_by_company/0712.HK.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,584 +662,636 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-550250</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-16201000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2201000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-2201000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-48383000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5862000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>151823000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-18402000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-24264000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-23440000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>24403000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>963000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-46732250</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-48383000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>183047000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1034830996</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1034830996</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-0.0468</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-0.0468</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-48383000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-48383000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-48383000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2140000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-50523000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-50523000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1856000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-48667000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>5108000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>-2201000</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="n">
-        <v>-774000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>2975000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-23440000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>24403000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>963000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-19883000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>31224000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>804000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>34593000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2156000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>32437000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>11341000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>151823000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>163164000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>163164000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="n">
+        <v>-745000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>15509500</v>
+        <v>1683000</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>-1513000</v>
+        <v>-33676000</v>
       </c>
       <c r="E3" t="n">
-        <v>62038000</v>
+        <v>13305000</v>
       </c>
       <c r="F3" t="n">
-        <v>62038000</v>
+        <v>6732000</v>
       </c>
       <c r="G3" t="n">
-        <v>44456000</v>
+        <v>-55805000</v>
       </c>
       <c r="H3" t="n">
-        <v>8667000</v>
+        <v>13803000</v>
       </c>
       <c r="I3" t="n">
-        <v>124061000</v>
+        <v>29329000</v>
       </c>
       <c r="J3" t="n">
-        <v>60525000</v>
+        <v>-20371000</v>
       </c>
       <c r="K3" t="n">
-        <v>51858000</v>
+        <v>-34174000</v>
       </c>
       <c r="L3" t="n">
-        <v>-13471000</v>
+        <v>-13887000</v>
       </c>
       <c r="M3" t="n">
-        <v>14032000</v>
+        <v>14017000</v>
       </c>
       <c r="N3" t="n">
-        <v>561000</v>
+        <v>130000</v>
       </c>
       <c r="O3" t="n">
-        <v>-2072500</v>
+        <v>-54281000</v>
       </c>
       <c r="P3" t="n">
-        <v>44456000</v>
+        <v>-55805000</v>
       </c>
       <c r="Q3" t="n">
-        <v>153845000</v>
+        <v>62830000</v>
       </c>
       <c r="R3" t="n">
-        <v>847096838</v>
+        <v>791709002</v>
       </c>
       <c r="S3" t="n">
-        <v>847096838</v>
+        <v>791709002</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0525</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0525</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>44456000</v>
+        <v>-55805000</v>
       </c>
       <c r="W3" t="n">
-        <v>44456000</v>
+        <v>-55805000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>44456000</v>
+        <v>-55805000</v>
       </c>
       <c r="Z3" t="n">
-        <v>1498000</v>
+        <v>-5116000</v>
       </c>
       <c r="AA3" t="n">
-        <v>42958000</v>
+        <v>-50689000</v>
       </c>
       <c r="AB3" t="n">
-        <v>42958000</v>
+        <v>-50689000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-5132000</v>
+        <v>2498000</v>
       </c>
       <c r="AD3" t="n">
-        <v>37826000</v>
+        <v>-48191000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2040000</v>
+        <v>7823000</v>
       </c>
       <c r="AF3" t="n">
-        <v>62038000</v>
+        <v>6732000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-68219000</v>
+        <v>6488000</v>
       </c>
       <c r="AH3" t="n">
-        <v>5493000</v>
+        <v>-24243000</v>
       </c>
       <c r="AI3" t="n">
-        <v>688000</v>
+        <v>4450000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-13471000</v>
+        <v>-13887000</v>
       </c>
       <c r="AK3" t="n">
-        <v>14032000</v>
+        <v>14017000</v>
       </c>
       <c r="AL3" t="n">
-        <v>561000</v>
+        <v>130000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-9200000</v>
+        <v>-25690000</v>
       </c>
       <c r="AN3" t="n">
-        <v>29784000</v>
+        <v>33501000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1158000</v>
+        <v>3400000</v>
       </c>
       <c r="AP3" t="n">
-        <v>32799000</v>
+        <v>40360000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2219000</v>
+        <v>4628000</v>
       </c>
       <c r="AR3" t="n">
-        <v>30580000</v>
+        <v>35732000</v>
       </c>
       <c r="AS3" t="n">
-        <v>20584000</v>
+        <v>7811000</v>
       </c>
       <c r="AT3" t="n">
-        <v>124061000</v>
+        <v>29329000</v>
       </c>
       <c r="AU3" t="n">
-        <v>144645000</v>
+        <v>37140000</v>
       </c>
       <c r="AV3" t="n">
-        <v>144645000</v>
+        <v>37140000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1683000</v>
+        <v>15509500</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>-33676000</v>
+        <v>-1513000</v>
       </c>
       <c r="E4" t="n">
-        <v>13305000</v>
+        <v>62038000</v>
       </c>
       <c r="F4" t="n">
-        <v>6732000</v>
+        <v>62038000</v>
       </c>
       <c r="G4" t="n">
-        <v>-55805000</v>
+        <v>44456000</v>
       </c>
       <c r="H4" t="n">
-        <v>13803000</v>
+        <v>8667000</v>
       </c>
       <c r="I4" t="n">
-        <v>29329000</v>
+        <v>124061000</v>
       </c>
       <c r="J4" t="n">
-        <v>-20371000</v>
+        <v>60525000</v>
       </c>
       <c r="K4" t="n">
-        <v>-34174000</v>
+        <v>51858000</v>
       </c>
       <c r="L4" t="n">
-        <v>-13887000</v>
+        <v>-13471000</v>
       </c>
       <c r="M4" t="n">
-        <v>14017000</v>
+        <v>14032000</v>
       </c>
       <c r="N4" t="n">
-        <v>130000</v>
+        <v>561000</v>
       </c>
       <c r="O4" t="n">
-        <v>-54281000</v>
+        <v>-2072500</v>
       </c>
       <c r="P4" t="n">
-        <v>-55805000</v>
+        <v>44456000</v>
       </c>
       <c r="Q4" t="n">
-        <v>62830000</v>
+        <v>153845000</v>
       </c>
       <c r="R4" t="n">
-        <v>791709002</v>
+        <v>847096838</v>
       </c>
       <c r="S4" t="n">
-        <v>791709002</v>
+        <v>847096838</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.0525</v>
       </c>
       <c r="V4" t="n">
-        <v>-55805000</v>
+        <v>44456000</v>
       </c>
       <c r="W4" t="n">
-        <v>-55805000</v>
+        <v>44456000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-55805000</v>
+        <v>44456000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-5116000</v>
+        <v>1498000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-50689000</v>
+        <v>42958000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-50689000</v>
+        <v>42958000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2498000</v>
+        <v>-5132000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-48191000</v>
+        <v>37826000</v>
       </c>
       <c r="AE4" t="n">
-        <v>7823000</v>
+        <v>2040000</v>
       </c>
       <c r="AF4" t="n">
-        <v>6732000</v>
+        <v>62038000</v>
       </c>
       <c r="AG4" t="n">
-        <v>6488000</v>
+        <v>-68219000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-24243000</v>
+        <v>5493000</v>
       </c>
       <c r="AI4" t="n">
-        <v>4450000</v>
+        <v>688000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-13887000</v>
+        <v>-13471000</v>
       </c>
       <c r="AK4" t="n">
-        <v>14017000</v>
+        <v>14032000</v>
       </c>
       <c r="AL4" t="n">
-        <v>130000</v>
+        <v>561000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-25690000</v>
+        <v>-9200000</v>
       </c>
       <c r="AN4" t="n">
-        <v>33501000</v>
+        <v>29784000</v>
       </c>
       <c r="AO4" t="n">
-        <v>3400000</v>
+        <v>1158000</v>
       </c>
       <c r="AP4" t="n">
-        <v>40360000</v>
+        <v>32799000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4628000</v>
+        <v>2219000</v>
       </c>
       <c r="AR4" t="n">
-        <v>35732000</v>
+        <v>30580000</v>
       </c>
       <c r="AS4" t="n">
-        <v>7811000</v>
+        <v>20584000</v>
       </c>
       <c r="AT4" t="n">
-        <v>29329000</v>
+        <v>124061000</v>
       </c>
       <c r="AU4" t="n">
-        <v>37140000</v>
+        <v>144645000</v>
       </c>
       <c r="AV4" t="n">
-        <v>37140000</v>
+        <v>144645000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-3634750</v>
+        <v>-550250</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>4171000</v>
+        <v>-16201000</v>
       </c>
       <c r="E5" t="n">
-        <v>-14539000</v>
+        <v>-2201000</v>
       </c>
       <c r="F5" t="n">
-        <v>-14539000</v>
+        <v>-2201000</v>
       </c>
       <c r="G5" t="n">
-        <v>-53196000</v>
+        <v>-48383000</v>
       </c>
       <c r="H5" t="n">
-        <v>19597000</v>
+        <v>5862000</v>
       </c>
       <c r="I5" t="n">
-        <v>48064000</v>
+        <v>151823000</v>
       </c>
       <c r="J5" t="n">
-        <v>-10368000</v>
+        <v>-18402000</v>
       </c>
       <c r="K5" t="n">
-        <v>-29965000</v>
+        <v>-24264000</v>
       </c>
       <c r="L5" t="n">
-        <v>-29930000</v>
+        <v>-23440000</v>
       </c>
       <c r="M5" t="n">
-        <v>29950000</v>
+        <v>24403000</v>
       </c>
       <c r="N5" t="n">
-        <v>20000</v>
+        <v>963000</v>
       </c>
       <c r="O5" t="n">
-        <v>-42291750</v>
+        <v>-46732250</v>
       </c>
       <c r="P5" t="n">
-        <v>-53196000</v>
+        <v>-48383000</v>
       </c>
       <c r="Q5" t="n">
-        <v>88821000</v>
+        <v>183047000</v>
       </c>
       <c r="R5" t="n">
-        <v>777104090</v>
+        <v>1034830996</v>
       </c>
       <c r="S5" t="n">
-        <v>777104090</v>
+        <v>1034830996</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0468</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.0468</v>
       </c>
       <c r="V5" t="n">
-        <v>-53196000</v>
+        <v>-48383000</v>
       </c>
       <c r="W5" t="n">
-        <v>-53196000</v>
+        <v>-48383000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-53196000</v>
+        <v>-48383000</v>
       </c>
       <c r="Z5" t="n">
-        <v>8056000</v>
+        <v>2140000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-61252000</v>
+        <v>-50523000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-61252000</v>
+        <v>-50523000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1337000</v>
+        <v>1856000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-59915000</v>
+        <v>-48667000</v>
       </c>
       <c r="AE5" t="n">
-        <v>11527000</v>
+        <v>5108000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-20807000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-745000</v>
-      </c>
+        <v>-2201000</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>22641000</v>
+        <v>-774000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-1089000</v>
+        <v>2975000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-29930000</v>
+        <v>-23440000</v>
       </c>
       <c r="AK5" t="n">
-        <v>29950000</v>
+        <v>24403000</v>
       </c>
       <c r="AL5" t="n">
-        <v>20000</v>
+        <v>963000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-33992000</v>
+        <v>-19883000</v>
       </c>
       <c r="AN5" t="n">
-        <v>40757000</v>
+        <v>31224000</v>
       </c>
       <c r="AO5" t="n">
-        <v>3439000</v>
+        <v>804000</v>
       </c>
       <c r="AP5" t="n">
-        <v>38158000</v>
+        <v>34593000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1224000</v>
+        <v>2156000</v>
       </c>
       <c r="AR5" t="n">
-        <v>36934000</v>
+        <v>32437000</v>
       </c>
       <c r="AS5" t="n">
-        <v>6765000</v>
+        <v>11341000</v>
       </c>
       <c r="AT5" t="n">
-        <v>48064000</v>
+        <v>151823000</v>
       </c>
       <c r="AU5" t="n">
-        <v>54829000</v>
+        <v>163164000</v>
       </c>
       <c r="AV5" t="n">
-        <v>54829000</v>
+        <v>163164000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-8150000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>897000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-32600000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-32600000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-63555000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2003000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>194008000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-31703000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-33706000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-28380000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>29805000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-39105000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-63555000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>224514000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1059923412</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1059923412</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-63555000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-63555000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-63555000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>715000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-64270000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-64270000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>759000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-63511000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>5721000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-32600000</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
+        <v>31646000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>954000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-28380000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>29805000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>-3280000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>30506000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1549000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>31464000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1578000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>29886000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>27226000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>194008000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>221234000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>221234000</v>
       </c>
     </row>
   </sheetData>
@@ -1253,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BT5"/>
+  <dimension ref="A1:BT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1615,345 +1667,221 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1059923412</v>
-      </c>
-      <c r="C2" t="n">
-        <v>1059923412</v>
-      </c>
-      <c r="D2" t="n">
-        <v>101237000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>121686000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-167353000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-57041000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-175884000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-167353000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>11374000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-167353000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-132682000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-160424000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6929000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-167353000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>118187000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-1993121000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1600933000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3727000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>3727000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>306683000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>47519000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2303000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1746000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>43470000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>8799000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>34671000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>259164000</v>
-      </c>
+        <v>31040000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>78216000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2575000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>75641000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>176076000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>117298000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>5859000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>52919000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>146259000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>62979000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1890000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>3528000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3528000</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
-        <v>4900000</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>4900000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>35126000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>17535000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-151686000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>169221000</v>
-      </c>
-      <c r="AZ2" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>915000</v>
+      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="n">
+        <v>1029000</v>
+      </c>
       <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>133087000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>33944000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>2190000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>83280000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>4369000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1090000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1057000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>33000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>34070000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>22166000</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>12505000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>-14620000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>27125000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>9075000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>9075000</v>
-      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>901581612</v>
+        <v>791709002</v>
       </c>
       <c r="C3" t="n">
-        <v>901581612</v>
+        <v>791709002</v>
       </c>
       <c r="D3" t="n">
-        <v>52502000</v>
+        <v>56549000</v>
       </c>
       <c r="E3" t="n">
-        <v>85999000</v>
+        <v>103504000</v>
       </c>
       <c r="F3" t="n">
-        <v>-133636000</v>
+        <v>-163436000</v>
       </c>
       <c r="G3" t="n">
-        <v>-62848000</v>
+        <v>-84343000</v>
       </c>
       <c r="H3" t="n">
-        <v>-157497000</v>
+        <v>-192258000</v>
       </c>
       <c r="I3" t="n">
-        <v>-133636000</v>
+        <v>-163436000</v>
       </c>
       <c r="J3" t="n">
-        <v>15211000</v>
+        <v>24411000</v>
       </c>
       <c r="K3" t="n">
-        <v>-133636000</v>
+        <v>-163436000</v>
       </c>
       <c r="L3" t="n">
-        <v>-99174000</v>
+        <v>-158736000</v>
       </c>
       <c r="M3" t="n">
-        <v>-134443000</v>
+        <v>-164153000</v>
       </c>
       <c r="N3" t="n">
-        <v>-807000</v>
+        <v>-717000</v>
       </c>
       <c r="O3" t="n">
-        <v>-133636000</v>
+        <v>-163436000</v>
       </c>
       <c r="P3" t="n">
         <v>118187000</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>31040000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1944587000</v>
+        <v>-1989043000</v>
       </c>
       <c r="S3" t="n">
-        <v>1586920000</v>
+        <v>1571637000</v>
       </c>
       <c r="T3" t="n">
-        <v>3153000</v>
+        <v>2752000</v>
       </c>
       <c r="U3" t="n">
-        <v>3153000</v>
+        <v>2752000</v>
       </c>
       <c r="V3" t="n">
-        <v>341480000</v>
+        <v>467099000</v>
       </c>
       <c r="W3" t="n">
-        <v>52328000</v>
+        <v>48830000</v>
       </c>
       <c r="X3" t="n">
-        <v>4810000</v>
+        <v>8983000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1746000</v>
+        <v>15278000</v>
       </c>
       <c r="Z3" t="n">
-        <v>45772000</v>
+        <v>24569000</v>
       </c>
       <c r="AA3" t="n">
-        <v>11310000</v>
+        <v>19869000</v>
       </c>
       <c r="AB3" t="n">
-        <v>34462000</v>
+        <v>4700000</v>
       </c>
       <c r="AC3" t="n">
-        <v>289152000</v>
-      </c>
-      <c r="AD3" t="inlineStr"/>
+        <v>418269000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>179500000</v>
+      </c>
       <c r="AE3" t="n">
-        <v>40227000</v>
+        <v>78935000</v>
       </c>
       <c r="AF3" t="n">
-        <v>3901000</v>
+        <v>4542000</v>
       </c>
       <c r="AG3" t="n">
-        <v>36326000</v>
+        <v>74393000</v>
       </c>
       <c r="AH3" t="n">
-        <v>241447000</v>
+        <v>152084000</v>
       </c>
       <c r="AI3" t="n">
-        <v>143555000</v>
+        <v>96089000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>5915000</v>
+        <v>5863000</v>
       </c>
       <c r="AK3" t="n">
-        <v>91977000</v>
+        <v>50132000</v>
       </c>
       <c r="AL3" t="n">
-        <v>207037000</v>
+        <v>302946000</v>
       </c>
       <c r="AM3" t="n">
-        <v>75382000</v>
+        <v>76935000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3672000</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>2873000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>2873000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>42660000</v>
+        <v>45093000</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
@@ -1963,20 +1891,22 @@
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>26177000</v>
+        <v>31842000</v>
       </c>
       <c r="AX3" t="n">
-        <v>-147168000</v>
+        <v>-138168000</v>
       </c>
       <c r="AY3" t="n">
-        <v>173345000</v>
+        <v>170010000</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
-      <c r="BA3" t="inlineStr"/>
+      <c r="BA3" t="n">
+        <v>31842000</v>
+      </c>
       <c r="BB3" t="n">
-        <v>137338000</v>
+        <v>134003000</v>
       </c>
       <c r="BC3" t="n">
         <v>33817000</v>
@@ -1988,180 +1918,184 @@
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>131655000</v>
+        <v>226011000</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>125358000</v>
       </c>
       <c r="BH3" t="n">
-        <v>0</v>
+        <v>204000</v>
       </c>
       <c r="BI3" t="n">
-        <v>21876000</v>
+        <v>36298000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1588000</v>
+        <v>3084000</v>
       </c>
       <c r="BK3" t="n">
-        <v>667000</v>
+        <v>1465000</v>
       </c>
       <c r="BL3" t="n">
-        <v>835000</v>
+        <v>1487000</v>
       </c>
       <c r="BM3" t="n">
-        <v>86000</v>
+        <v>132000</v>
       </c>
       <c r="BN3" t="n">
-        <v>18731000</v>
+        <v>9036000</v>
       </c>
       <c r="BO3" t="n">
-        <v>23689000</v>
+        <v>23514000</v>
       </c>
       <c r="BP3" t="n">
-        <v>47485000</v>
+        <v>5973000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-15232000</v>
+        <v>-32614000</v>
       </c>
       <c r="BR3" t="n">
-        <v>62717000</v>
+        <v>38587000</v>
       </c>
       <c r="BS3" t="n">
-        <v>18286000</v>
+        <v>22544000</v>
       </c>
       <c r="BT3" t="n">
-        <v>18286000</v>
+        <v>22544000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>791709002</v>
+        <v>901581612</v>
       </c>
       <c r="C4" t="n">
-        <v>791709002</v>
+        <v>901581612</v>
       </c>
       <c r="D4" t="n">
-        <v>56549000</v>
+        <v>52502000</v>
       </c>
       <c r="E4" t="n">
-        <v>103504000</v>
+        <v>85999000</v>
       </c>
       <c r="F4" t="n">
-        <v>-163436000</v>
+        <v>-133636000</v>
       </c>
       <c r="G4" t="n">
-        <v>-84343000</v>
+        <v>-62848000</v>
       </c>
       <c r="H4" t="n">
-        <v>-192258000</v>
+        <v>-157497000</v>
       </c>
       <c r="I4" t="n">
-        <v>-163436000</v>
+        <v>-133636000</v>
       </c>
       <c r="J4" t="n">
-        <v>24411000</v>
+        <v>15211000</v>
       </c>
       <c r="K4" t="n">
-        <v>-163436000</v>
+        <v>-133636000</v>
       </c>
       <c r="L4" t="n">
-        <v>-158736000</v>
+        <v>-99174000</v>
       </c>
       <c r="M4" t="n">
-        <v>-164153000</v>
+        <v>-134443000</v>
       </c>
       <c r="N4" t="n">
-        <v>-717000</v>
+        <v>-807000</v>
       </c>
       <c r="O4" t="n">
-        <v>-163436000</v>
+        <v>-133636000</v>
       </c>
       <c r="P4" t="n">
         <v>118187000</v>
       </c>
       <c r="Q4" t="n">
-        <v>31040000</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-1989043000</v>
+        <v>-1944587000</v>
       </c>
       <c r="S4" t="n">
-        <v>1571637000</v>
+        <v>1586920000</v>
       </c>
       <c r="T4" t="n">
-        <v>2752000</v>
+        <v>3153000</v>
       </c>
       <c r="U4" t="n">
-        <v>2752000</v>
+        <v>3153000</v>
       </c>
       <c r="V4" t="n">
-        <v>467099000</v>
+        <v>341480000</v>
       </c>
       <c r="W4" t="n">
-        <v>48830000</v>
+        <v>52328000</v>
       </c>
       <c r="X4" t="n">
-        <v>8983000</v>
+        <v>4810000</v>
       </c>
       <c r="Y4" t="n">
-        <v>15278000</v>
+        <v>1746000</v>
       </c>
       <c r="Z4" t="n">
-        <v>24569000</v>
+        <v>45772000</v>
       </c>
       <c r="AA4" t="n">
-        <v>19869000</v>
+        <v>11310000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4700000</v>
+        <v>34462000</v>
       </c>
       <c r="AC4" t="n">
-        <v>418269000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>179500000</v>
-      </c>
+        <v>289152000</v>
+      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>78935000</v>
+        <v>40227000</v>
       </c>
       <c r="AF4" t="n">
-        <v>4542000</v>
+        <v>3901000</v>
       </c>
       <c r="AG4" t="n">
-        <v>74393000</v>
+        <v>36326000</v>
       </c>
       <c r="AH4" t="n">
-        <v>152084000</v>
+        <v>241447000</v>
       </c>
       <c r="AI4" t="n">
-        <v>96089000</v>
+        <v>143555000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5863000</v>
+        <v>5915000</v>
       </c>
       <c r="AK4" t="n">
-        <v>50132000</v>
+        <v>91977000</v>
       </c>
       <c r="AL4" t="n">
-        <v>302946000</v>
+        <v>207037000</v>
       </c>
       <c r="AM4" t="n">
-        <v>76935000</v>
+        <v>75382000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>3672000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
+        <v>2873000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2873000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
       <c r="AS4" t="n">
-        <v>45093000</v>
+        <v>42660000</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
@@ -2171,22 +2105,20 @@
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>31842000</v>
+        <v>26177000</v>
       </c>
       <c r="AX4" t="n">
-        <v>-138168000</v>
+        <v>-147168000</v>
       </c>
       <c r="AY4" t="n">
-        <v>170010000</v>
+        <v>173345000</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
-      <c r="BA4" t="n">
-        <v>31842000</v>
-      </c>
+      <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="n">
-        <v>134003000</v>
+        <v>137338000</v>
       </c>
       <c r="BC4" t="n">
         <v>33817000</v>
@@ -2198,255 +2130,463 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>226011000</v>
+        <v>131655000</v>
       </c>
       <c r="BG4" t="n">
-        <v>125358000</v>
+        <v>0</v>
       </c>
       <c r="BH4" t="n">
-        <v>204000</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>36298000</v>
+        <v>21876000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>3084000</v>
+        <v>1588000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1465000</v>
+        <v>667000</v>
       </c>
       <c r="BL4" t="n">
-        <v>1487000</v>
+        <v>835000</v>
       </c>
       <c r="BM4" t="n">
-        <v>132000</v>
+        <v>86000</v>
       </c>
       <c r="BN4" t="n">
-        <v>9036000</v>
+        <v>18731000</v>
       </c>
       <c r="BO4" t="n">
-        <v>23514000</v>
+        <v>23689000</v>
       </c>
       <c r="BP4" t="n">
-        <v>5973000</v>
+        <v>47485000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-32614000</v>
+        <v>-15232000</v>
       </c>
       <c r="BR4" t="n">
-        <v>38587000</v>
+        <v>62717000</v>
       </c>
       <c r="BS4" t="n">
-        <v>22544000</v>
+        <v>18286000</v>
       </c>
       <c r="BT4" t="n">
-        <v>22544000</v>
+        <v>18286000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>791709002</v>
+        <v>1059923412</v>
       </c>
       <c r="C5" t="n">
-        <v>791709002</v>
+        <v>1059923412</v>
       </c>
       <c r="D5" t="n">
-        <v>187024000</v>
+        <v>101237000</v>
       </c>
       <c r="E5" t="n">
-        <v>203670000</v>
+        <v>121686000</v>
       </c>
       <c r="F5" t="n">
-        <v>-115119000</v>
+        <v>-167353000</v>
       </c>
       <c r="G5" t="n">
-        <v>86161000</v>
+        <v>-57041000</v>
       </c>
       <c r="H5" t="n">
-        <v>-313453000</v>
+        <v>-175884000</v>
       </c>
       <c r="I5" t="n">
-        <v>-115119000</v>
+        <v>-167353000</v>
       </c>
       <c r="J5" t="n">
-        <v>9878000</v>
+        <v>11374000</v>
       </c>
       <c r="K5" t="n">
-        <v>-107631000</v>
+        <v>-167353000</v>
       </c>
       <c r="L5" t="n">
-        <v>-100131000</v>
+        <v>-132682000</v>
       </c>
       <c r="M5" t="n">
-        <v>-113464000</v>
+        <v>-160424000</v>
       </c>
       <c r="N5" t="n">
-        <v>-5833000</v>
+        <v>6929000</v>
       </c>
       <c r="O5" t="n">
-        <v>-107631000</v>
+        <v>-167353000</v>
       </c>
       <c r="P5" t="n">
         <v>118187000</v>
       </c>
       <c r="Q5" t="n">
-        <v>31040000</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>-1933212000</v>
+        <v>-1993121000</v>
       </c>
       <c r="S5" t="n">
-        <v>1571637000</v>
+        <v>1600933000</v>
       </c>
       <c r="T5" t="n">
-        <v>2752000</v>
+        <v>3727000</v>
       </c>
       <c r="U5" t="n">
-        <v>2752000</v>
+        <v>3727000</v>
       </c>
       <c r="V5" t="n">
-        <v>405353000</v>
+        <v>306683000</v>
       </c>
       <c r="W5" t="n">
-        <v>34568000</v>
+        <v>47519000</v>
       </c>
       <c r="X5" t="n">
-        <v>6489000</v>
+        <v>2303000</v>
       </c>
       <c r="Y5" t="n">
-        <v>12826000</v>
+        <v>1746000</v>
       </c>
       <c r="Z5" t="n">
-        <v>15253000</v>
+        <v>43470000</v>
       </c>
       <c r="AA5" t="n">
-        <v>7753000</v>
+        <v>8799000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7500000</v>
+        <v>34671000</v>
       </c>
       <c r="AC5" t="n">
-        <v>370785000</v>
+        <v>259164000</v>
       </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>188417000</v>
+        <v>78216000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2125000</v>
+        <v>2575000</v>
       </c>
       <c r="AG5" t="n">
-        <v>186292000</v>
+        <v>75641000</v>
       </c>
       <c r="AH5" t="n">
-        <v>175148000</v>
+        <v>176076000</v>
       </c>
       <c r="AI5" t="n">
-        <v>102560000</v>
+        <v>117298000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5829000</v>
+        <v>5859000</v>
       </c>
       <c r="AK5" t="n">
-        <v>66759000</v>
+        <v>52919000</v>
       </c>
       <c r="AL5" t="n">
-        <v>291889000</v>
+        <v>146259000</v>
       </c>
       <c r="AM5" t="n">
-        <v>234557000</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+        <v>62979000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1890000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3528000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3528000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>4900000</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>4900000</v>
       </c>
       <c r="AS5" t="n">
-        <v>127362000</v>
+        <v>35126000</v>
       </c>
       <c r="AT5" t="n">
-        <v>7488000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>915000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>6573000</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>99707000</v>
+        <v>17535000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-175897000</v>
+        <v>-151686000</v>
       </c>
       <c r="AY5" t="n">
-        <v>275604000</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1029000</v>
-      </c>
+        <v>169221000</v>
+      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>180022000</v>
+        <v>133087000</v>
       </c>
       <c r="BC5" t="n">
-        <v>82845000</v>
+        <v>33944000</v>
       </c>
       <c r="BD5" t="n">
-        <v>11708000</v>
+        <v>2190000</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>57332000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
+        <v>83280000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>137000</v>
+        <v>5000</v>
       </c>
       <c r="BI5" t="n">
-        <v>39778000</v>
+        <v>4369000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>3163000</v>
+        <v>1090000</v>
       </c>
       <c r="BK5" t="n">
-        <v>793000</v>
+        <v>1057000</v>
       </c>
       <c r="BL5" t="n">
-        <v>1739000</v>
+        <v>33000</v>
       </c>
       <c r="BM5" t="n">
-        <v>631000</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>39778000</v>
-      </c>
-      <c r="BO5" t="inlineStr"/>
+        <v>34070000</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>22166000</v>
+      </c>
       <c r="BP5" t="n">
-        <v>7486000</v>
+        <v>12505000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-55836000</v>
+        <v>-14620000</v>
       </c>
       <c r="BR5" t="n">
-        <v>63322000</v>
+        <v>27125000</v>
       </c>
       <c r="BS5" t="n">
-        <v>6768000</v>
+        <v>9075000</v>
       </c>
       <c r="BT5" t="n">
-        <v>6768000</v>
+        <v>9075000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1059923412</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1059923412</v>
+      </c>
+      <c r="D6" t="n">
+        <v>163621000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>176423000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-230397000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-62518000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-251155000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-230397000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8544000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-230397000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-201272000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-223690000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6707000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-230397000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>118187000</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>-2056676000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1600933000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3727000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3727000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>644443000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>40425000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1816000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2379000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>36230000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7105000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>29125000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>604018000</v>
+      </c>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>140193000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1439000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>138754000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>440248000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>149268000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>5868000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>285112000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>420753000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>67890000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1890000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>4532000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4532000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4900000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>30477000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>26091000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>-150427000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>176518000</v>
+      </c>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>128871000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>33944000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>13703000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>352863000</v>
+      </c>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>63218000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>132964000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>132434000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>530000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>61926000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>36968000</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>53524000</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>-45518000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>99042000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>4258000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>4258000</v>
       </c>
     </row>
   </sheetData>
@@ -2460,7 +2600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT5"/>
+  <dimension ref="A1:AT6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2692,162 +2832,104 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-10806000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-4845000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8358000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>9075000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>18286000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-9211000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>887000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>-671000</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>-4594000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>8358000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8358000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1155000</v>
-      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
-        <v>1155000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>-4845000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>708000</v>
-      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-5000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>963000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-250000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
-        <v>-250000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-10806000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-130000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2199000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-940000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-46604000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>498000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>49245000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>19267000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>5862000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>5862000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7534000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>928000</v>
-      </c>
+        <v>21077000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="n">
+        <v>1220000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="n">
-        <v>-48667000</v>
-      </c>
+      <c r="AS2" t="n">
+        <v>-745000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-22015000</v>
+        <v>137475000</v>
       </c>
       <c r="C3" t="n">
-        <v>-13487000</v>
+        <v>-119212000</v>
       </c>
       <c r="D3" t="n">
-        <v>41763000</v>
+        <v>10000</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-3690000</v>
+        <v>-223000</v>
       </c>
       <c r="G3" t="n">
-        <v>18286000</v>
+        <v>22544000</v>
       </c>
       <c r="H3" t="n">
-        <v>22544000</v>
+        <v>6768000</v>
       </c>
       <c r="I3" t="n">
-        <v>-4258000</v>
+        <v>15776000</v>
       </c>
       <c r="J3" t="n">
-        <v>18492000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>735000</v>
-      </c>
+        <v>-131762000</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>-1409000</v>
+        <v>-8770000</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -2856,130 +2938,134 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>28276000</v>
+        <v>-119202000</v>
       </c>
       <c r="P3" t="n">
-        <v>-3600000</v>
+        <v>-13000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3600000</v>
+        <v>-13000000</v>
       </c>
       <c r="R3" t="n">
-        <v>28276000</v>
+        <v>-106202000</v>
       </c>
       <c r="S3" t="n">
-        <v>-13487000</v>
+        <v>-106212000</v>
       </c>
       <c r="T3" t="n">
-        <v>41763000</v>
+        <v>10000</v>
       </c>
       <c r="U3" t="n">
-        <v>-4425000</v>
+        <v>9840000</v>
       </c>
       <c r="V3" t="n">
-        <v>204000</v>
+        <v>-67000</v>
       </c>
       <c r="W3" t="n">
-        <v>561000</v>
+        <v>130000</v>
       </c>
       <c r="X3" t="n">
-        <v>-1500000</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="n">
-        <v>-1500000</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>-3690000</v>
+        <v>9777000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3690000</v>
+        <v>-223000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-18325000</v>
+        <v>137698000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-161000</v>
+        <v>-12000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-13699000</v>
+        <v>162769000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-272000</v>
+        <v>186697000</v>
       </c>
       <c r="AH3" t="n">
-        <v>50550000</v>
+        <v>-21384000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1496000</v>
+        <v>79000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-65473000</v>
+        <v>-2623000</v>
       </c>
       <c r="AK3" t="n">
-        <v>9208000</v>
+        <v>21912000</v>
       </c>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="n">
-        <v>8667000</v>
+        <v>13803000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>915000</v>
       </c>
       <c r="AO3" t="n">
-        <v>8667000</v>
+        <v>12888000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2433000</v>
+        <v>-3187000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-651000</v>
+        <v>3843000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-68129000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>-19000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
       <c r="AT3" t="n">
-        <v>37826000</v>
+        <v>-48191000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>137475000</v>
+        <v>-22015000</v>
       </c>
       <c r="C4" t="n">
-        <v>-119212000</v>
+        <v>-13487000</v>
       </c>
       <c r="D4" t="n">
-        <v>10000</v>
+        <v>41763000</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-223000</v>
+        <v>-3690000</v>
       </c>
       <c r="G4" t="n">
+        <v>18286000</v>
+      </c>
+      <c r="H4" t="n">
         <v>22544000</v>
       </c>
-      <c r="H4" t="n">
-        <v>6768000</v>
-      </c>
       <c r="I4" t="n">
-        <v>15776000</v>
+        <v>-4258000</v>
       </c>
       <c r="J4" t="n">
-        <v>-131762000</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
+        <v>18492000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>735000</v>
+      </c>
       <c r="L4" t="n">
-        <v>-8770000</v>
+        <v>-1409000</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -2988,228 +3074,336 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-119202000</v>
+        <v>28276000</v>
       </c>
       <c r="P4" t="n">
-        <v>-13000000</v>
+        <v>-3600000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-13000000</v>
+        <v>-3600000</v>
       </c>
       <c r="R4" t="n">
-        <v>-106202000</v>
+        <v>28276000</v>
       </c>
       <c r="S4" t="n">
-        <v>-106212000</v>
+        <v>-13487000</v>
       </c>
       <c r="T4" t="n">
-        <v>10000</v>
+        <v>41763000</v>
       </c>
       <c r="U4" t="n">
-        <v>9840000</v>
+        <v>-4425000</v>
       </c>
       <c r="V4" t="n">
-        <v>-67000</v>
+        <v>204000</v>
       </c>
       <c r="W4" t="n">
-        <v>130000</v>
+        <v>561000</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1500000</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-1500000</v>
       </c>
       <c r="AA4" t="n">
-        <v>9777000</v>
+        <v>-3690000</v>
       </c>
       <c r="AB4" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-223000</v>
+        <v>-3690000</v>
       </c>
       <c r="AD4" t="n">
-        <v>137698000</v>
+        <v>-18325000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-12000</v>
+        <v>-161000</v>
       </c>
       <c r="AF4" t="n">
-        <v>162769000</v>
+        <v>-13699000</v>
       </c>
       <c r="AG4" t="n">
-        <v>186697000</v>
+        <v>-272000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-21384000</v>
+        <v>50550000</v>
       </c>
       <c r="AI4" t="n">
-        <v>79000</v>
+        <v>1496000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-2623000</v>
+        <v>-65473000</v>
       </c>
       <c r="AK4" t="n">
-        <v>21912000</v>
+        <v>9208000</v>
       </c>
       <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>13803000</v>
+        <v>8667000</v>
       </c>
       <c r="AN4" t="n">
-        <v>915000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>12888000</v>
+        <v>8667000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-3187000</v>
+        <v>2433000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3843000</v>
+        <v>-651000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-19000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
+        <v>-68129000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>-48191000</v>
+        <v>37826000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>935000</v>
+        <v>-10806000</v>
       </c>
       <c r="C5" t="n">
-        <v>-44475000</v>
+        <v>-4845000</v>
       </c>
       <c r="D5" t="n">
-        <v>25549000</v>
+        <v>6000000</v>
       </c>
       <c r="E5" t="n">
-        <v>3120000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-671000</v>
-      </c>
+        <v>8358000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>6768000</v>
+        <v>9075000</v>
       </c>
       <c r="H5" t="n">
-        <v>5126000</v>
+        <v>18286000</v>
       </c>
       <c r="I5" t="n">
-        <v>1642000</v>
+        <v>-9211000</v>
       </c>
       <c r="J5" t="n">
-        <v>-20390000</v>
+        <v>887000</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>-1990000</v>
+        <v>-4594000</v>
       </c>
       <c r="M5" t="n">
-        <v>3120000</v>
+        <v>8358000</v>
       </c>
       <c r="N5" t="n">
-        <v>3120000</v>
+        <v>8358000</v>
       </c>
       <c r="O5" t="n">
-        <v>-18926000</v>
+        <v>1155000</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
-        <v>-18926000</v>
+        <v>1155000</v>
       </c>
       <c r="S5" t="n">
-        <v>-44475000</v>
+        <v>-4845000</v>
       </c>
       <c r="T5" t="n">
-        <v>25549000</v>
+        <v>6000000</v>
       </c>
       <c r="U5" t="n">
-        <v>20426000</v>
+        <v>708000</v>
       </c>
       <c r="V5" t="n">
-        <v>21077000</v>
+        <v>-5000</v>
       </c>
       <c r="W5" t="n">
-        <v>20000</v>
+        <v>963000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>-250000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="n">
+        <v>-250000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>-671000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-671000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1606000</v>
+        <v>-10806000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-31000</v>
+        <v>-130000</v>
       </c>
       <c r="AF5" t="n">
-        <v>4129000</v>
+        <v>2199000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-13038000</v>
+        <v>-940000</v>
       </c>
       <c r="AH5" t="n">
-        <v>14082000</v>
+        <v>-46604000</v>
       </c>
       <c r="AI5" t="n">
-        <v>12135000</v>
+        <v>498000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-9050000</v>
+        <v>49245000</v>
       </c>
       <c r="AK5" t="n">
-        <v>29090000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
+        <v>19267000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>19597000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1220000</v>
-      </c>
+        <v>5862000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>18377000</v>
+        <v>5862000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-11408000</v>
+        <v>7534000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-663000</v>
+        <v>928000</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
-      <c r="AS5" t="n">
-        <v>-745000</v>
-      </c>
+      <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>-59915000</v>
+        <v>-48667000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-59600000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-5214000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>64244000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-11513000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4258000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9075000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-4817000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>53358000</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>-2842000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>59030000</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>59030000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-5214000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>64244000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-10088000</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>-11513000</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="n">
+        <v>-11513000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-48087000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-117000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-47750000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>20725000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>237571000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-131874000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>-174172000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>25873000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="n">
+        <v>2003000</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>2003000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>4649000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>-1834000</v>
+      </c>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="n">
+        <v>-63511000</v>
       </c>
     </row>
   </sheetData>
@@ -3223,7 +3417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI2"/>
+  <dimension ref="A1:EL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3289,635 +3483,650 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>fullTimeEmployees</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>companyOfficers</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>compensationAsOfEpochDate</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>executiveTeam</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>maxAge</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>priceHint</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>previousClose</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>dayLow</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>dayHigh</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>regularMarketPreviousClose</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>regularMarketOpen</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>regularMarketDayLow</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>regularMarketDayHigh</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>exDividendDate</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>payoutRatio</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>beta</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>forwardPE</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>bidSize</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>askSize</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>forwardEps</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>pegRatio</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>lastSplitFactor</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>lastSplitDate</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>lastDividendValue</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>lastDividendDate</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>freeCashflow</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>operatingCashflow</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3981,438 +4190,447 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Comtec Solar Systems Group Limited, an investment holding company, provides logistics services to the factories, manufacturers, raw material providers in the People's Republic of China and Hong Kong. The company operates in two segments, Solar and Power Storage, and Logistics Services. It offers consulting services for investment, development, construction, and operation of solar photovoltaic power stations; and produces and sells of power storage, lithium battery, and mono-crystalline products. The company also provides polysilicon, pseudo square bricks, and wafers; and solar engineering, procurement, and construction (EPC) services. In addition, it researches and develops, designs, integrates, and sells lithium battery management; production and sales of lithium battery power storage systems to electric vehicle and power storage customers; produces and sells power storage products; and engages in the operation of rooftop distributed power generation projects in industrial, commercial, and residential buildings. Further, the company provides sourcing, invoicing, and support services. Comtec Solar Systems Group Limited was founded in 1999 and is headquartered in Changzhou, the People's Republic of China.</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
+          <t>Comtec Solar Systems Group Limited, together with its subsidiaries, engages in the research, design, development, manufacturing, marketing, and sale of semiconductor wafers in the People's Republic of China and Hong Kong. The company operates in two segments, Solar and Power Storage, and Logistics Services. It offers mono-crystalline, power storage, and lithium battery products, as well as solar grade products, including pseudo square bricks, wafers, and polysilicon. The company also provides consulting services for investment, development, construction, and operation of solar photovoltaic power stations; and logistics services to factories, manufacturers, and raw material providers. In addition, it is involved in the provision of sourcing, invoicing, and support services. The company was founded in 1999 and is headquartered in Changzhou, China.</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>67</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>[{'maxAge': 1, 'name': 'Mr. Yi  Zhang', 'age': 62, 'title': 'Executive Chairman', 'yearBorn': 1963, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xiaoxi  Che', 'age': 36, 'title': 'VP &amp; COO', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Sing Wai  Yuen', 'age': 36, 'title': 'Company Secretary', 'yearBorn': 1989, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>86400</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>3</v>
       </c>
-      <c r="R2" t="n">
-        <v>0.078</v>
-      </c>
       <c r="S2" t="n">
-        <v>0.083</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.083</v>
+        <v>0.062</v>
       </c>
       <c r="V2" t="n">
-        <v>0.078</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.083</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>0.077</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.083</v>
+        <v>0.062</v>
       </c>
       <c r="Z2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1273795200</v>
       </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
       <c r="AB2" t="n">
-        <v>0.615</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.42777777</v>
+        <v>0.603</v>
       </c>
       <c r="AD2" t="n">
-        <v>450000</v>
+        <v>-0.37777779</v>
       </c>
       <c r="AE2" t="n">
-        <v>450000</v>
+        <v>155000</v>
       </c>
       <c r="AF2" t="n">
-        <v>406983</v>
+        <v>155000</v>
       </c>
       <c r="AG2" t="n">
-        <v>481100</v>
+        <v>322141</v>
       </c>
       <c r="AH2" t="n">
-        <v>481100</v>
+        <v>111200</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.07199999999999999</v>
+        <v>111200</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.081</v>
+        <v>0.064</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>81614104</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>82674026</v>
+        <v>72074792</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.07000000000000001</v>
+        <v>72074792</v>
       </c>
       <c r="AP2" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>0.189</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AR2" t="n">
         <v>19.2</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AS2" t="n">
         <v>0.06</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0.368904</v>
-      </c>
       <c r="AT2" t="n">
-        <v>0.09374</v>
+        <v>0.32578534</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.11408</v>
+        <v>0.0882</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>0.112245</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="inlineStr">
         <is>
           <t>HKD</t>
         </is>
       </c>
-      <c r="AY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>98374104</v>
+      <c r="AZ2" t="b">
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
+        <v>258366256</v>
+      </c>
+      <c r="BB2" t="n">
         <v>-0.28728</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BC2" t="n">
         <v>532431328</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BD2" t="n">
         <v>1059923412</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>0.49767</v>
       </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
       <c r="BF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG2" t="n">
         <v>1059923412</v>
       </c>
-      <c r="BG2" t="n">
-        <v>-0.25131676</v>
-      </c>
       <c r="BH2" t="n">
+        <v>-0.25134218</v>
+      </c>
+      <c r="BI2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BK2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>-63555000</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BM2" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BN2" t="n">
         <v>-0.18</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BO2" t="n">
         <v>0.71</v>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>1:4</t>
         </is>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>1566950400</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>0.445</v>
-      </c>
       <c r="BR2" t="n">
-        <v>-2.897</v>
+        <v>1.168</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.03999996</v>
+        <v>-7.099</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.27294624</v>
+        <v>-0.09333330400000001</v>
       </c>
       <c r="BU2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="BV2" t="n">
         <v>0.0332</v>
       </c>
-      <c r="BV2" t="n">
+      <c r="BW2" t="n">
         <v>1273795200</v>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BX2" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BY2" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BZ2" t="n">
-        <v>166370000</v>
-      </c>
       <c r="CA2" t="n">
-        <v>0.157</v>
+        <v>4258000</v>
       </c>
       <c r="CB2" t="n">
-        <v>-33963000</v>
+        <v>0.004</v>
       </c>
       <c r="CC2" t="n">
+        <v>-36397000</v>
+      </c>
+      <c r="CD2" t="n">
         <v>176423008</v>
       </c>
-      <c r="CD2" t="n">
-        <v>0.364</v>
-      </c>
       <c r="CE2" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="CF2" t="n">
         <v>0.584</v>
       </c>
-      <c r="CF2" t="n">
+      <c r="CG2" t="n">
         <v>221234000</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CH2" t="n">
         <v>0.209</v>
       </c>
-      <c r="CH2" t="n">
-        <v>-0.08252</v>
-      </c>
       <c r="CI2" t="n">
+        <v>-0.08087</v>
+      </c>
+      <c r="CJ2" t="n">
         <v>27226000</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CK2" t="n">
+        <v>-42589248</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-48087000</v>
+      </c>
+      <c r="CM2" t="n">
         <v>-0.046</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CN2" t="n">
         <v>0.123059995</v>
       </c>
-      <c r="CL2" t="n">
-        <v>-0.15352</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>-0.35671002</v>
-      </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="n">
+        <v>-0.16452</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>-0.34645998</v>
+      </c>
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>0712.HK</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="CX2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="CV2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CW2" t="n">
+      <c r="CY2" t="n">
+        <v>-2.857138</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>Comtec Solar Systems Group Limited</t>
+        </is>
+      </c>
+      <c r="DC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DD2" t="n">
         <v>1256866200000</v>
       </c>
-      <c r="CX2" t="n">
-        <v>-0.001000002</v>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>0.077 - 0.083</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DE2" t="n">
+        <v>-0.0019999966</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>0.062 - 0.07</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>COMTEC SOLAR</t>
+        </is>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>1781768838</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>finmb_78410896</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>406983</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>0.0069999993</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>0.09999999</v>
-      </c>
-      <c r="DD2" t="inlineStr">
-        <is>
-          <t>0.07 - 0.189</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>-0.111999996</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>-0.5925926</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>3.9999962</v>
-      </c>
-      <c r="DH2" t="n">
+      <c r="DR2" t="n">
+        <v>322141</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.0060000047</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.09677427</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>0.062 - 0.189</t>
+        </is>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.12099999</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.64021164</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-9.33333</v>
+      </c>
+      <c r="DY2" t="n">
         <v>1743458715</v>
       </c>
-      <c r="DI2" t="n">
+      <c r="DZ2" t="n">
         <v>1743458715</v>
       </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="n">
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="EC2" t="n">
         <v>-0.18</v>
       </c>
-      <c r="DM2" t="n">
-        <v>-0.016740002</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>-0.17857906</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.037079997</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.32503504</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.30638626</v>
-      </c>
-      <c r="DR2" t="n">
+      <c r="ED2" t="n">
+        <v>-0.0202</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.22902493</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.044244997</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.39418235</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.2705475</v>
+      </c>
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EJ2" t="n">
         <v>15</v>
       </c>
-      <c r="DT2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-1.2820538</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>COMTEC SOLAR</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>Comtec Solar Systems Group Limited</t>
-        </is>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>1780386588</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>finmb_78410896</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="inlineStr"/>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
